--- a/data/b2_candoi/B2 Candói 12-2025.xlsx
+++ b/data/b2_candoi/B2 Candói 12-2025.xlsx
@@ -4959,151 +4959,151 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>45996</v>
+        <v>45993</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>57781.49</v>
+        <v>2571.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>45998</v>
+        <v>45996</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>3603.6</v>
+        <v>57780.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46001</v>
+        <v>45998</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>3200</v>
+        <v>1778.18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46003</v>
+        <v>45998</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1105.05</v>
+        <v>3821.69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46005</v>
+        <v>46001</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4112.21</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>8936.83</v>
+        <v>838.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46006</v>
+        <v>46004</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1206.63</v>
+        <v>1098.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46011</v>
+        <v>46005</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>20305.78</v>
+        <v>1845.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46012</v>
+        <v>46005</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -5116,66 +5116,66 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>3526.03</v>
+        <v>3922.35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1140.31</v>
+        <v>9123.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46016</v>
+        <v>46006</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Fretes</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Frete das entregas de combustível</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>9460</v>
+        <v>1059.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46016</v>
+        <v>46011</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>3558.45</v>
+        <v>20228.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46016</v>
+        <v>46011</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -5184,47 +5184,47 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1027.71</v>
+        <v>1024.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46017</v>
+        <v>46012</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2557.59</v>
+        <v>3916.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46017</v>
+        <v>46016</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Fretes</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Frete das entregas de combustível</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1624.33</v>
+        <v>9460</v>
       </c>
     </row>
     <row r="17">
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3784.73</v>
+        <v>3866.63</v>
       </c>
     </row>
     <row r="18">
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>1622.96</v>
+        <v>1525.93</v>
       </c>
     </row>
   </sheetData>
